--- a/stories/arbres/ATOM-SOC.ARG.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ce matin, papa a fini son travail. Il rentre avec son sac. Léa l'attend près de la porte. Papa dit : j'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Léa et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Léa porte la baguette tiède. Ensuite, les légumes. Des carottes. Des tomates. Papa dit : l'argent sert aussi aux légumes. Léa pose une carotte dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire. Il dit : l'argent sert aux chaussures, quand on en a besoin. Léa touche le cuir souple. Papa range le reste de l'argent. Léa dit : le travail de papa sert à acheter. Pain. Légumes. Chaussures.</t>
+          <t>Ce matin, papa a fini son travail. Il rentre avec son sac. Léa l'attend près de la porte. J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Léa et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Léa porte la baguette tiède. Ensuite, les légumes. Des carottes. Des tomates. L'argent sert aussi aux légumes. Léa pose une carotte dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire. L'argent sert aux chaussures, quand on en a besoin. Léa touche le cuir souple. Papa range le reste de l'argent. Le travail de papa sert à acheter. Pain. Légumes. Chaussures.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ce matin, papa a fini son travail. Il rentre avec son sac. Léa l'attend près de la porte.
+papa|J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter.
+narrateur|Léa et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Léa porte la baguette tiède. Ensuite, les légumes. Des carottes. Des tomates.
+papa|L'argent sert aussi aux légumes.
+narrateur|Léa pose une carotte dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire.
+narrateur|L'argent sert aux chaussures, quand on en a besoin.
+narrateur|Léa touche le cuir souple. Papa range le reste de l'argent.
+enfant-f|Le travail de papa sert à acheter. Pain. Légumes. Chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa a travaillé. L'argent sert à quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a compris. Le travail de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|À la maison, Léa pose le pain sur la table. Papa range les légumes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 enfant-f|Le travail de papa sert à acheter. Pain. Légumes. Chaussures.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Papa a travaillé. L'argent sert à quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Léa a compris. Le travail de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|À la maison, Léa pose le pain sur la table. Papa range les légumes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.ARG.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L'argent du marché de Léa</t>
+          <t>Le petit pain chaud de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Au marché sous la bâche, Mila veut un petit pain chaud. Celui qu'elle montre est déjà vendu. Papa paie un autre, encore tiède. Elle croque la mie.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ce matin, papa a fini son travail. Il rentre avec son sac. Léa l'attend près de la porte. J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Léa et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Léa porte la baguette tiède. Ensuite, les légumes. Des carottes. Des tomates. L'argent sert aussi aux légumes. Léa pose une carotte dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire. L'argent sert aux chaussures, quand on en a besoin. Léa touche le cuir souple. Papa range le reste de l'argent. Le travail de papa sert à acheter. Pain. Légumes. Chaussures.</t>
+          <t>La bâche du marché sent la farine chaude. Un pigeon picore une miette grise. Les caisses de bois sont encore humides. Ça sent le beurre et le café. Papa range une pièce dans sa poche. Mila vit ici, avec papa. Papa, ça sent le four ! Oui. Le stand du pain est ouvert. Je veux un petit pain chaud. Le rond, bien doré ? Oui. En ce moment, Mila tient le cabas. Le tissu râpe un peu ses doigts. Elles avancent sous la bâche. La vitrine du stand est pleine. Des petits pains dorés alignés. Celui-là, le bien doré ! Tu le montres du doigt ? Oui. Mila montre le petit pain du milieu. Il brille encore un peu. Une main le prend, plus loin. Le pain part dans un autre sac. Il n'est plus là. Il est déjà vendu. On en prend un autre ? Encore chaud ? Oui. Papa montre un pain tout près. La croûte est plus claire, encore tiède. Celui-là. J'ai une pièce, dans la poche. Elle sert à prendre le pain. Papa tend la pièce. La pièce sonne dans le tiroir. Le tiroir se ferme, tout court. Le petit pain passe dans le cabas. Il est chaud ! Oui. Tu le tiens ? Oui, papa. Mila pose les deux mains autour. La croûte pique un peu les paumes. Ça sent le four, tout près. Tu as fini de le sentir ? Presque.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ce matin, papa a fini son &lt;emphasis level="moderate"&gt;travail&lt;/emphasis&gt;. Il rentre avec son sac. Léa l'attend près de la porte. Papa dit : j'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter. Léa et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Léa porte la baguette tiède. Ensuite, les légumes. Des carottes. Des tomates. Papa dit : l'argent sert aussi aux légumes. Léa pose une carotte dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire. Il dit : l'argent sert aux chaussures, quand on en a besoin. Léa touche le cuir souple. Papa range le reste de l'argent. Léa dit : le travail de papa sert à acheter. Pain. Légumes. Chaussures.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La bâche du marché sent la farine chaude. Un pigeon picore une miette grise. Les caisses de bois sont encore humides. Ça sent le beurre et le café. Papa range une pièce dans sa poche. Mila vit ici, avec papa. Papa, ça sent le four ! Oui. Le stand du pain est ouvert. Je veux un petit pain chaud. Le rond, bien doré ? Oui. En ce moment, Mila tient le cabas. Le tissu râpe un peu ses doigts. Elles avancent sous la bâche. La vitrine du stand est pleine. Des petits pains dorés alignés. Celui-là, le bien doré ! Tu le montres du doigt ? Oui. Mila montre le petit pain du milieu. Il brille encore un peu. Une main le prend, plus loin. Le pain part dans un autre sac. Il n'est plus là. Il est déjà vendu. On en prend un autre ? Encore chaud ? Oui. Papa montre un pain tout près. La croûte est plus claire, encore tiède. Celui-là. J'ai une pièce, dans la poche. Elle sert à prendre le pain. Papa tend la pièce. La pièce sonne dans le tiroir. Le tiroir se ferme, tout court. Le petit pain passe dans le cabas. Il est chaud ! Oui. Tu le tiens ? Oui, papa. Mila pose les deux mains autour. La croûte pique un peu les paumes. Ça sent le four, tout près. Tu as fini de le sentir ? Presque.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,17 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ce matin, papa a fini son travail. Il rentre avec son sac. Léa l'attend près de la porte.
-papa|J'ai travaillé. Avec le travail, on a de l'argent. L'argent sert à acheter.
-narrateur|Léa et papa vont au marché. D'abord, le stand du pain. Papa donne l'argent. Il peut acheter du pain. Léa porte la baguette tiède. Ensuite, les légumes. Des carottes. Des tomates.
-papa|L'argent sert aussi aux légumes.
-narrateur|Léa pose une carotte dans le cabas. Plus loin, il y a des chaussures. Papa montre une paire.
-narrateur|L'argent sert aux chaussures, quand on en a besoin.
-narrateur|Léa touche le cuir souple. Papa range le reste de l'argent.
-enfant-f|Le travail de papa sert à acheter. Pain. Légumes. Chaussures.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La bâche du marché sent la farine chaude.
+narrateur|Un pigeon picore une miette grise.
+narrateur|Les caisses de bois sont encore humides.
+narrateur|Ça sent le beurre et le café.
+narrateur|Papa range une pièce dans sa poche.
+narrateur|Mila vit ici, avec papa.
+enfant-f|Papa, ça sent le four !
+papa|Oui.
+papa|Le stand du pain est ouvert.
+enfant-f|Je veux un petit pain chaud.
+papa|Le rond, bien doré ?
+enfant-f|Oui.
+narrateur|En ce moment, Mila tient le cabas.
+narrateur|Le tissu râpe un peu ses doigts.
+narrateur|Elles avancent sous la bâche.
+narrateur|La vitrine du stand est pleine.
+narrateur|Des petits pains dorés alignés.
+enfant-f|Celui-là, le bien doré !
+papa|Tu le montres du doigt ?
+enfant-f|Oui.
+narrateur|Mila montre le petit pain du milieu.
+narrateur|Il brille encore un peu.
+narrateur|Une main le prend, plus loin.
+narrateur|Le pain part dans un autre sac.
+enfant-f|Il n'est plus là.
+papa|Il est déjà vendu.
+papa|On en prend un autre ?
+enfant-f|Encore chaud ?
+papa|Oui.
+narrateur|Papa montre un pain tout près.
+narrateur|La croûte est plus claire, encore tiède.
+enfant-f|Celui-là.
+papa|J'ai une pièce, dans la poche.
+papa|Elle sert à prendre le pain.
+narrateur|Papa tend la pièce.
+narrateur|La pièce sonne dans le tiroir.
+narrateur|Le tiroir se ferme, tout court.
+narrateur|Le petit pain passe dans le cabas.
+enfant-f|Il est chaud !
+papa|Oui.
+papa|Tu le tiens ?
+enfant-f|Oui, papa.
+narrateur|Mila pose les deux mains autour.
+narrateur|La croûte pique un peu les paumes.
+narrateur|Ça sent le four, tout près.
+papa|Tu as fini de le sentir ?
+enfant-f|Presque.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,12 +1397,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa a travaillé. L'argent sert à quoi ?</t>
+          <t>Papa a donné une pièce. L'argent sert à quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa a &lt;emphasis level="moderate"&gt;travail&lt;/emphasis&gt;lé. L'argent sert à quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a donné une pièce. L'argent sert à quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,7 +1417,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>acheter | le pain | acheter du pain | le travail</t>
+          <t>acheter | le pain | le petit pain | prendre le pain | la pièce</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1432,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On achète du pain. L'argent sert à quoi ?</t>
+          <t>On prend le petit pain. L'argent sert à quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1431,7 +1481,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1557,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa a travaillé. L'argent sert à quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Papa a donné une pièce.
+narrateur|L'argent sert à quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a compris. Le travail de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
+          <t>Le petit pain est dans les mains de Mila. Il chauffe encore les doigts. La pièce a servi à le prendre. Pour le pain chaud. Oui. On achète le pain avec ça. Une graine tombe sur le cabas. Mila la pose sur la croûte. Elle est restée. Oui. Tu as choisi l'autre pain. Bravo, Mila. Le pigeon n'a plus de miette. La bâche claque un peu au vent. Le cabas sent le four, tout fort. On rentre ? Oui. Mila garde le pain contre elle. La croûte fait un petit bruit. Il est encore chaud, non ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa a compris. Le &lt;emphasis level="moderate"&gt;travail&lt;/emphasis&gt; de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit pain est dans les mains de Mila. Il chauffe encore les doigts. La pièce a servi à le prendre. Pour le pain chaud. Oui. On achète le pain avec ça. Une graine tombe sur le cabas. Mila la pose sur la croûte. Elle est restée. Oui. Tu as choisi l'autre pain. Bravo, Mila. Le pigeon n'a plus de miette. La bâche claque un peu au vent. Le cabas sent le four, tout fort. On rentre ? Oui. Mila garde le pain contre elle. La croûte fait un petit bruit. Il est encore chaud, non ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1603,7 +1653,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,10 +1729,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a compris. Le travail de papa sert. L'argent sert à acheter. Pain. Légumes. Chaussures.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le petit pain est dans les mains de Mila.
+narrateur|Il chauffe encore les doigts.
+papa|La pièce a servi à le prendre.
+enfant-f|Pour le pain chaud.
+papa|Oui.
+papa|On achète le pain avec ça.
+narrateur|Une graine tombe sur le cabas.
+narrateur|Mila la pose sur la croûte.
+enfant-f|Elle est restée.
+papa|Oui.
+papa|Tu as choisi l'autre pain.
+papa|Bravo, Mila.
+narrateur|Le pigeon n'a plus de miette.
+narrateur|La bâche claque un peu au vent.
+narrateur|Le cabas sent le four, tout fort.
+papa|On rentre ?
+enfant-f|Oui.
+narrateur|Mila garde le pain contre elle.
+narrateur|La croûte fait un petit bruit.
+papa|Il est encore chaud, non ?
+enfant-f|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1776,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>À la maison, Léa pose le pain sur la table. Papa range les légumes.</t>
+          <t>La porte de la maison claque doucement. La table de bois est froide. Tu poses le pain ? Oui. Mila pose le petit pain au milieu. Une petite vapeur monte encore. Il fume ! Oui. Merci d'avoir tenu le cabas. Papa coupe le pain en deux. La mie est blanche, toute douce. Je goûte ? Un morceau, tout petit. Mila croque un coin. Ça croustille, puis c'est tiède. C'est bon. Le four était encore allumé. La graine reste collée à sa lèvre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;À la maison, Léa pose le pain sur la table. Papa range les légumes.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La porte de la maison claque doucement. La table de bois est froide. Tu poses le pain ? Oui. Mila pose le petit pain au milieu. Une petite vapeur monte encore. Il fume ! Oui. Merci d'avoir tenu le cabas. Papa coupe le pain en deux. La mie est blanche, toute douce. Je goûte ? Un morceau, tout petit. Mila croque un coin. Ça croustille, puis c'est tiède. C'est bon. Le four était encore allumé. La graine reste collée à sa lèvre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1775,7 +1844,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1843,10 +1912,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|À la maison, Léa pose le pain sur la table. Papa range les légumes.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La porte de la maison claque doucement.
+narrateur|La table de bois est froide.
+papa|Tu poses le pain ?
+enfant-f|Oui.
+narrateur|Mila pose le petit pain au milieu.
+narrateur|Une petite vapeur monte encore.
+enfant-f|Il fume !
+papa|Oui.
+papa|Merci d'avoir tenu le cabas.
+narrateur|Papa coupe le pain en deux.
+narrateur|La mie est blanche, toute douce.
+enfant-f|Je goûte ?
+papa|Un morceau, tout petit.
+narrateur|Mila croque un coin.
+narrateur|Ça croustille, puis c'est tiède.
+enfant-f|C'est bon.
+papa|Le four était encore allumé.
+narrateur|La graine reste collée à sa lèvre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1871,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le premier était vendu. On a pris l'autre, chaud. Bravo, Mila. La mie sent encore le four. Le petit pain chauffe encore sa main.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le premier était vendu. On a pris l'autre, chaud. Bravo, Mila. La mie sent encore le four. Le petit pain chauffe encore sa main.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1932,14 +2017,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2011,10 +2096,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Le premier était vendu.
+enfant-f|On a pris l'autre, chaud.
+papa|Bravo, Mila.
+narrateur|La mie sent encore le four.
+narrateur|Le petit pain chauffe encore sa main.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2159,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché</t>
+          <t>marché sous la bâche, stand du pain, cabas de toile</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
